--- a/reports/member_funnel/downloads/member_funnel_1y_target_vip.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_vip.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>veritaskm</t>
+          <t>kk_2905067716</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01084555847</t>
+          <t>01099172715</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDM_0220</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_2905067716</t>
+          <t>kk_4201213646</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01099172715</t>
+          <t>01027969918</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_ECOM_cart_sale</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3215602159</t>
+          <t>kk_2933318514</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01050406700</t>
+          <t>01048004176</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CSC1938 Dually Mountain Outerchange</t>
+          <t>Centrillium 2.5L Jacket</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,27 +1071,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_2933318514</t>
+          <t>kk_4548582000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01048004176</t>
+          <t>01099254539</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Centrillium 2.5L Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,12 +1103,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4548582000</t>
+          <t>kk_4614369618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01099254539</t>
+          <t>01093720985</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's Stone Dash Fleece Jacket</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,27 +1135,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4614369618</t>
+          <t>jsy3689</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01093720985</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>M's Stone Dash Fleece Jacket</t>
+          <t>Acker Rock Twill SS Button Down</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,27 +1167,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jsy3689</t>
+          <t>idlsb</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01031293827</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Acker Rock Twill SS Button Down</t>
+          <t>M's Cow Mountain Cargo Straight Pants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,12 +1199,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>idlsb</t>
+          <t>swsga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01031293827</t>
+          <t>01090067664</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>M's Cow Mountain Cargo Straight Pants</t>
+          <t>M's 365 Mountain II Shirts Jacket</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>swsga</t>
+          <t>insoule1201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01090067664</t>
+          <t>01024461707</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M's 365 Mountain II Shirts Jacket</t>
+          <t>Centrillium Jacket</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>insoule1201</t>
+          <t>rnjsrldn135</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01024461707</t>
+          <t>01033756034</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Centrillium Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rnjsrldn135</t>
+          <t>kk_4787402711</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01033756034</t>
+          <t>01022018682</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's Lee Hike Jacket</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4787402711</t>
+          <t>kk_3876211678</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01022018682</t>
+          <t>01038900880</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>M's Lee Hike Jacket</t>
+          <t>Centrillium II Jacket</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3876211678</t>
+          <t>kk_4830354827</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01038900880</t>
+          <t>01058470790</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Centrillium II Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,27 +1391,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4830354827</t>
+          <t>likjky1207</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01058470790</t>
+          <t>01028547812</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>likjky1207</t>
+          <t>hee615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01028547812</t>
+          <t>01077099356</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,27 +1455,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hee615</t>
+          <t>rokmc8375</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01077099356</t>
+          <t>01033942995</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>M's Tonto Dome Detachable Down Jacket</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,27 +1487,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rokmc8375</t>
+          <t>jhmun150102</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01033942995</t>
+          <t>01029758998</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>M's Tonto Dome Detachable Down Jacket</t>
+          <t>M's Dana Cove OFZ ICE Straight Pants</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,27 +1519,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>jhmun150102</t>
+          <t>camino</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01029758998</t>
+          <t>01099009610</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>M's Dana Cove OFZ ICE Straight Pants</t>
+          <t>W's Cow Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>camino</t>
+          <t>bulls3005</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01099009610</t>
+          <t>01030830402</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>W's Cow Mountain 2L Jacket</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1583,27 +1583,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bulls3005</t>
+          <t>kk_4563468909</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01030830402</t>
+          <t>01050047528</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1615,27 +1615,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4563468909</t>
+          <t>bluewolf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01050047528</t>
+          <t>01022741671</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
+          <t>Silver Ridge 3.0 LS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,12 +1647,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bluewolf</t>
+          <t>kk_4738944549</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01022741671</t>
+          <t>01077475609</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Silver Ridge 3.0 LS</t>
+          <t>W’s 365 Mountain II Pants</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,27 +1679,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4738944549</t>
+          <t>nudyrody</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01077475609</t>
+          <t>01054493261</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>W’s 365 Mountain II Pants</t>
+          <t>Street Transit III Backpack</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nudyrody</t>
+          <t>kk_2866660043</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01054493261</t>
+          <t>01055776347</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Street Transit III Backpack</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_2866660043</t>
+          <t>starbeau</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01055776347</t>
+          <t>01046449575</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>JAAWAA WP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>starbeau</t>
+          <t>varta70</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01046449575</t>
+          <t>01090324458</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>JAAWAA WP</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1807,27 +1807,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>varta70</t>
+          <t>kk_4668470247</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01090324458</t>
+          <t>01091704352</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>Acker Rock Windbreaker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4668470247</t>
+          <t>sjyaksh</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01091704352</t>
+          <t>01028146042</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Acker Rock Windbreaker</t>
+          <t>REDWOOD™30 N.PLUS BACKPACK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1871,12 +1871,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sjyaksh</t>
+          <t>skykibo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01028146042</t>
+          <t>01087401745</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>REDWOOD™30 N.PLUS BACKPACK</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>skykibo</t>
+          <t>kk_3207099024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01087401745</t>
+          <t>01089831542</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1935,27 +1935,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_3207099024</t>
+          <t>ksy0418</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01089831542</t>
+          <t>01044882829</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1967,27 +1967,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ksy0418</t>
+          <t>kk_4518224758</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01044882829</t>
+          <t>01053836007</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
+          <t>Reign No Shine Jacket</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1999,12 +1999,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4518224758</t>
+          <t>eoqkf2350</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01053836007</t>
+          <t>01085132350</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_MESSAGE_0226_NEWARRIVAL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reign No Shine Jacket</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2031,27 +2031,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>eoqkf2350</t>
+          <t>kk_4769273093</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01085132350</t>
+          <t>01052131666</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_NEWARRIVAL</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4769273093</t>
+          <t>kk_4817740812</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01052131666</t>
+          <t>01055834285</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2095,27 +2095,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4817740812</t>
+          <t>kk_3358593705</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01055834285</t>
+          <t>01092418450</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's Nina Trail Insulation Straight Pants</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2127,27 +2127,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3358593705</t>
+          <t>bs0459</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01092418450</t>
+          <t>01054684752</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>M's Nina Trail Insulation Straight Pants</t>
+          <t>REDWOOD™30 N.PLUS BACKPACK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2159,27 +2159,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bs0459</t>
+          <t>gusegunjy</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01054684752</t>
+          <t>01050184903</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>REDWOOD™30 N.PLUS BACKPACK</t>
+          <t>M's Dart Forest Corduroy Shirts</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2191,27 +2191,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>gusegunjy</t>
+          <t>kk_4701110516</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01050184903</t>
+          <t>01035216142</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>M's Dart Forest Corduroy Shirts</t>
+          <t>M's Pines to Avenue Insulation Jacket</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2223,27 +2223,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4701110516</t>
+          <t>welko33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01035216142</t>
+          <t>01052950560</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>M's Pines to Avenue Insulation Jacket</t>
+          <t>W's Fawn Peak Down Jacket</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2255,27 +2255,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>welko33</t>
+          <t>finehill70</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01052950560</t>
+          <t>01038914568</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_1024_NEW_MEN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>W's Fawn Peak Down Jacket</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2287,27 +2287,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>finehill70</t>
+          <t>jabinim03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01038914568</t>
+          <t>01023317100</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1024_NEW_MEN</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>Light Canyon Soft Shell Jacket</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jabinim03</t>
+          <t>jsb8508</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01023317100</t>
+          <t>01095103236</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Light Canyon Soft Shell Jacket</t>
+          <t>Acker Rock Convertible Pant</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2351,27 +2351,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jsb8508</t>
+          <t>k03815</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01095103236</t>
+          <t>01036470014</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Acker Rock Convertible Pant</t>
+          <t>CSC1938 V1 Hoodie</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>k03815</t>
+          <t>exworks</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01036470014</t>
+          <t>01025771323</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CSC1938 V1 Hoodie</t>
+          <t>MONTRAIL TRINITY AG II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2415,12 +2415,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>exworks</t>
+          <t>kk_4002283474</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01025771323</t>
+          <t>01064231241</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_1024_NEW_MEN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MONTRAIL TRINITY AG II</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4002283474</t>
+          <t>kk_2956373067</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01064231241</t>
+          <t>01095975788</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1024_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Acker Rock Twill Interchange Jacket</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2479,27 +2479,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_2956373067</t>
+          <t>samjong9288</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01095975788</t>
+          <t>01029817798</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Acker Rock Twill Interchange Jacket</t>
+          <t>Ms Shotover Hill™ Insulation Jacket</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2511,27 +2511,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>samjong9288</t>
+          <t>kk_4322116727</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01029817798</t>
+          <t>01056335862</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ms Shotover Hill™ Insulation Jacket</t>
+          <t>REDWOOD™30 N.PLUS BACKPACK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2543,27 +2543,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4322116727</t>
+          <t>kk_3650630650</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01056335862</t>
+          <t>01092692024</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>REDWOOD™30 N.PLUS BACKPACK</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3650630650</t>
+          <t>uok1812</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01092692024</t>
+          <t>01062327111</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>Centrillium 2.5L Jacket</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2607,27 +2607,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>uok1812</t>
+          <t>litelf9</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01062327111</t>
+          <t>01026258089</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Centrillium 2.5L Jacket</t>
+          <t>M's Columbia Rock Long Down Jacket</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2639,27 +2639,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>litelf9</t>
+          <t>js0166</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01026258089</t>
+          <t>01054257658</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>M's Columbia Rock Long Down Jacket</t>
+          <t>ROC Tech 5 Pocket Pant</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2671,27 +2671,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>js0166</t>
+          <t>woo84111</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01054257658</t>
+          <t>01047853204</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ROC Tech 5 Pocket Pant</t>
+          <t>M's English Hike OFZ ICE Set Up Straight Pants</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2703,12 +2703,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>woo84111</t>
+          <t>swyang1015</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01047853204</t>
+          <t>01046994278</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>M's English Hike OFZ ICE Set Up Straight Pants</t>
+          <t>Centrillium 2.5L Jacket</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2735,12 +2735,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>swyang1015</t>
+          <t>dbstn2209</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01046994278</t>
+          <t>01094532239</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naversa_pc</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Centrillium 2.5L Jacket</t>
+          <t>M's Three Rock Jacket</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dbstn2209</t>
+          <t>ddong7277</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01094532239</t>
+          <t>01092947277</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>M's Three Rock Jacket</t>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ddong7277</t>
+          <t>legend1924</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01092947277</t>
+          <t>01031937259</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>M's Avoca Trail Down Jacket</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2831,12 +2831,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>legend1924</t>
+          <t>syim0418</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01031937259</t>
+          <t>01084183611</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>M's Avoca Trail Down Jacket</t>
+          <t>PEAKFREAK RUSH MID OUTDRY</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2863,27 +2863,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>syim0418</t>
+          <t>kk_3730552596</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01084183611</t>
+          <t>01062281122</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH MID OUTDRY</t>
+          <t>Silver Ridge Elite Convertible Pant</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_3730552596</t>
+          <t>kk_4769064058</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01062281122</t>
+          <t>01067600913</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Convertible Pant</t>
+          <t>Light Canyon Soft Shell Jacket</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2927,27 +2927,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4769064058</t>
+          <t>kk_4739745581</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01067600913</t>
+          <t>01071348866</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Light Canyon Soft Shell Jacket</t>
+          <t>M’s Adventure 365 LW Down Jacket</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4739745581</t>
+          <t>kk_4771786173</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01071348866</t>
+          <t>01052392267</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>M’s Adventure 365 LW Down Jacket</t>
+          <t>M's Dart Forest Corduroy Shirts</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2991,12 +2991,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4771786173</t>
+          <t>yjh033</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01052392267</t>
+          <t>01042417759</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>M's Dart Forest Corduroy Shirts</t>
+          <t>CSC1938 Dually Mountain Outerchange</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3023,27 +3023,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>yjh033</t>
+          <t>lilac7</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01042417759</t>
+          <t>01063741355</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CSC1938 Dually Mountain Outerchange</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3055,27 +3055,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lilac7</t>
+          <t>kk_4751091386</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01063741355</t>
+          <t>01020284421</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>Little Grey Ridge™ Jacket</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3087,27 +3087,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4751091386</t>
+          <t>kk_2957156524</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01020284421</t>
+          <t>01058529304</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Little Grey Ridge™ Jacket</t>
+          <t>W's Point to Crest Knit Set Up Jacket</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3119,12 +3119,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_2957156524</t>
+          <t>kk_4737706934</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01058529304</t>
+          <t>01034357111</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>W's Point to Crest Knit Set Up Jacket</t>
+          <t>M's Nina Trail Insulation Straight Pants</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3151,27 +3151,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4737706934</t>
+          <t>ryu6504</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01034357111</t>
+          <t>01044807214</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>M's Nina Trail Insulation Straight Pants</t>
+          <t>CRESTWOOD™ WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3183,27 +3183,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ryu6504</t>
+          <t>kk_4485262782</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01044807214</t>
+          <t>01050917710</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CRESTWOOD™ WATERPROOF WIDE</t>
+          <t>PFG Unted™ Insulated Anorak</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4485262782</t>
+          <t>mini10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01050917710</t>
+          <t>01092172140</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PFG Unted™ Insulated Anorak</t>
+          <t>M's Rolling Cone Long Down Jacket</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3247,12 +3247,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mini10</t>
+          <t>kk_4749552264</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01092172140</t>
+          <t>01093027496</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>M's Rolling Cone Long Down Jacket</t>
+          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3279,12 +3279,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4749552264</t>
+          <t>kk_4737589827</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01093027496</t>
+          <t>01065854092</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
+          <t>CRESTWOOD MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3311,12 +3311,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4737589827</t>
+          <t>kk_4738137983</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01065854092</t>
+          <t>01026622946</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CRESTWOOD MID WATERPROOF WIDE</t>
+          <t>M's Lee Hike Jacket</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3343,27 +3343,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4738137983</t>
+          <t>kk_2924032291</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01026622946</t>
+          <t>01045600173</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>M's Lee Hike Jacket</t>
+          <t>Ms Victoria Loop™ Long Down Jacket</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3375,12 +3375,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_2924032291</t>
+          <t>kk_4740134952</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01045600173</t>
+          <t>01026523530</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ms Victoria Loop™ Long Down Jacket</t>
+          <t>SAPLAND IV WP OMNI-HEAT INFINITY</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3407,27 +3407,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4740134952</t>
+          <t>kk_4494354762</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01026523530</t>
+          <t>01054222956</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SAPLAND IV WP OMNI-HEAT INFINITY</t>
+          <t>PEAKFREAK RUSH™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3439,27 +3439,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4494354762</t>
+          <t>ywcreateme</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01054222956</t>
+          <t>01086974559</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH™ OUTDRY™ WIDE</t>
+          <t>M's Stone Dash Fleece Straight Pants</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3471,12 +3471,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ywcreateme</t>
+          <t>phyjazz</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01086974559</t>
+          <t>01074464005</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>M's Stone Dash Fleece Straight Pants</t>
+          <t>M's Hocking Rim Insulation Straight Pants</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>phyjazz</t>
+          <t>kk_4727272523</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01074464005</t>
+          <t>01094511283</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3518,47 +3518,15 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>M's Hocking Rim Insulation Straight Pants</t>
+          <t>SAPLAND IV WP OMNI-HEAT INFINITY</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
-        <is>
-          <t>VIP_EXCLUSIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>kk_4727272523</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>01094511283</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>SAPLAND IV WP OMNI-HEAT INFINITY</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
         <is>
           <t>VIP_EXCLUSIVE</t>
         </is>
